--- a/week-01/Petal & Pastry Customer Feedback Survey (1-7).xlsx
+++ b/week-01/Petal & Pastry Customer Feedback Survey (1-7).xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -3027,88 +3027,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB8D78E8-0C87-4794-95E2-203AB570AC44}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A21:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="8">
-        <item x="3"/>
-        <item x="4"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Name" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AE2C11CE-5E89-4E2D-BAA1-C883613B8487}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="13">
@@ -3176,6 +3094,88 @@
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB8D78E8-0C87-4794-95E2-203AB570AC44}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A21:B25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="13">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Name" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
